--- a/data/file_generation/reference/data_75/研究二 - 后测共情测量原始数据导出 - 数字编码 - 已转换选项_res.xlsx
+++ b/data/file_generation/reference/data_75/研究二 - 后测共情测量原始数据导出 - 数字编码 - 已转换选项_res.xlsx
@@ -4587,26 +4587,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01436AE7-484A-4348-8748-0132E0D59B31}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A293DDC-E7D0-471B-A92B-41FB295051A5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BBAA2D7-AEB7-4B85-8877-4A6461F629F8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A65E1824-B874-4EEB-8792-BF247CD293C1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{874B8864-CA02-4368-8F02-C81CC69B7B20}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{349A04F4-B9EE-4979-98CA-52CFEE7DB894}"/>
 </file>